--- a/data/indicator_scores.xlsx
+++ b/data/indicator_scores.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -18736,7 +18736,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -19055,7 +19055,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -24478,7 +24478,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -25116,7 +25116,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -25754,7 +25754,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -26711,7 +26711,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -27030,7 +27030,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -27987,7 +27987,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -28625,7 +28625,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
@@ -28944,7 +28944,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -29263,7 +29263,7 @@
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
@@ -29582,7 +29582,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -29901,7 +29901,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -30220,7 +30220,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
@@ -30539,7 +30539,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -30858,7 +30858,7 @@
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -31177,7 +31177,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -31815,7 +31815,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
@@ -32134,7 +32134,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -32453,7 +32453,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
@@ -32772,7 +32772,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
@@ -33410,7 +33410,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
@@ -33729,7 +33729,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
@@ -34048,7 +34048,7 @@
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
@@ -34367,7 +34367,7 @@
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1171" t="inlineStr">
@@ -34686,7 +34686,7 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
@@ -35005,7 +35005,7 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
@@ -35324,7 +35324,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
@@ -35643,7 +35643,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1215" t="inlineStr">
@@ -35962,7 +35962,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
@@ -36281,7 +36281,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -36919,7 +36919,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -37238,7 +37238,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
@@ -37557,7 +37557,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1281" t="inlineStr">
@@ -37876,7 +37876,7 @@
       </c>
       <c r="C1292" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1292" t="inlineStr">
@@ -38195,7 +38195,7 @@
       </c>
       <c r="C1303" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1303" t="inlineStr">
@@ -38514,7 +38514,7 @@
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1314" t="inlineStr">
@@ -38833,7 +38833,7 @@
       </c>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1325" t="inlineStr">
@@ -39152,7 +39152,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1336" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1347" t="inlineStr">
@@ -39790,7 +39790,7 @@
       </c>
       <c r="C1358" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1358" t="inlineStr">
@@ -40109,7 +40109,7 @@
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1369" t="inlineStr">
@@ -40428,7 +40428,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1380" t="inlineStr">
@@ -40747,7 +40747,7 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr">
@@ -41066,7 +41066,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1402" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr">
@@ -41704,7 +41704,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
@@ -42023,7 +42023,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
@@ -42342,7 +42342,7 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
@@ -42661,7 +42661,7 @@
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -42980,7 +42980,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
@@ -43618,7 +43618,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="C1501" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1501" t="inlineStr">
@@ -44256,7 +44256,7 @@
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr">
@@ -44575,7 +44575,7 @@
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
@@ -44894,7 +44894,7 @@
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
@@ -45213,7 +45213,7 @@
       </c>
       <c r="C1545" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1545" t="inlineStr">
@@ -45532,7 +45532,7 @@
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
@@ -45851,7 +45851,7 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
@@ -46170,7 +46170,7 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
@@ -46489,7 +46489,7 @@
       </c>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
@@ -46808,7 +46808,7 @@
       </c>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr">
@@ -47127,7 +47127,7 @@
       </c>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr">
@@ -47446,7 +47446,7 @@
       </c>
       <c r="C1622" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1622" t="inlineStr">
@@ -47765,7 +47765,7 @@
       </c>
       <c r="C1633" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1633" t="inlineStr">
@@ -48084,7 +48084,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1644" t="inlineStr">
@@ -48403,7 +48403,7 @@
       </c>
       <c r="C1655" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1655" t="inlineStr">
@@ -48722,7 +48722,7 @@
       </c>
       <c r="C1666" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1666" t="inlineStr">
@@ -49041,7 +49041,7 @@
       </c>
       <c r="C1677" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1677" t="inlineStr">
@@ -49360,7 +49360,7 @@
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1688" t="inlineStr">
@@ -49679,7 +49679,7 @@
       </c>
       <c r="C1699" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1699" t="inlineStr">
@@ -49998,7 +49998,7 @@
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1710" t="inlineStr">
@@ -50317,7 +50317,7 @@
       </c>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1721" t="inlineStr">
@@ -50636,7 +50636,7 @@
       </c>
       <c r="C1732" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1732" t="inlineStr">
@@ -50955,7 +50955,7 @@
       </c>
       <c r="C1743" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1743" t="inlineStr">
@@ -51274,7 +51274,7 @@
       </c>
       <c r="C1754" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1754" t="inlineStr">
@@ -51593,7 +51593,7 @@
       </c>
       <c r="C1765" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1765" t="inlineStr">
@@ -51912,7 +51912,7 @@
       </c>
       <c r="C1776" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1776" t="inlineStr">
@@ -52231,7 +52231,7 @@
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1787" t="inlineStr">
@@ -52550,7 +52550,7 @@
       </c>
       <c r="C1798" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1798" t="inlineStr">
@@ -52869,7 +52869,7 @@
       </c>
       <c r="C1809" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1809" t="inlineStr">
@@ -53188,7 +53188,7 @@
       </c>
       <c r="C1820" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1820" t="inlineStr">
@@ -53507,7 +53507,7 @@
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1831" t="inlineStr">
@@ -53826,7 +53826,7 @@
       </c>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1842" t="inlineStr">
@@ -54145,7 +54145,7 @@
       </c>
       <c r="C1853" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1853" t="inlineStr">
@@ -54464,7 +54464,7 @@
       </c>
       <c r="C1864" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1864" t="inlineStr">
@@ -54783,7 +54783,7 @@
       </c>
       <c r="C1875" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1875" t="inlineStr">
@@ -55102,7 +55102,7 @@
       </c>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
@@ -55421,7 +55421,7 @@
       </c>
       <c r="C1897" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1897" t="inlineStr">
@@ -55740,7 +55740,7 @@
       </c>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1908" t="inlineStr">
@@ -56059,7 +56059,7 @@
       </c>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
@@ -56378,7 +56378,7 @@
       </c>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1930" t="inlineStr">
@@ -56697,7 +56697,7 @@
       </c>
       <c r="C1941" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1941" t="inlineStr">
@@ -57016,7 +57016,7 @@
       </c>
       <c r="C1952" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1952" t="inlineStr">
@@ -57335,7 +57335,7 @@
       </c>
       <c r="C1963" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1963" t="inlineStr">
@@ -57654,7 +57654,7 @@
       </c>
       <c r="C1974" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1974" t="inlineStr">
@@ -57973,7 +57973,7 @@
       </c>
       <c r="C1985" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1985" t="inlineStr">
@@ -58292,7 +58292,7 @@
       </c>
       <c r="C1996" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D1996" t="inlineStr">
@@ -58611,7 +58611,7 @@
       </c>
       <c r="C2007" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2007" t="inlineStr">
@@ -58930,7 +58930,7 @@
       </c>
       <c r="C2018" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2018" t="inlineStr">
@@ -59249,7 +59249,7 @@
       </c>
       <c r="C2029" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2029" t="inlineStr">
@@ -59568,7 +59568,7 @@
       </c>
       <c r="C2040" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2040" t="inlineStr">
@@ -59887,7 +59887,7 @@
       </c>
       <c r="C2051" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2051" t="inlineStr">
@@ -60206,7 +60206,7 @@
       </c>
       <c r="C2062" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2062" t="inlineStr">
@@ -60525,7 +60525,7 @@
       </c>
       <c r="C2073" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2073" t="inlineStr">
@@ -60844,7 +60844,7 @@
       </c>
       <c r="C2084" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2084" t="inlineStr">
@@ -61163,7 +61163,7 @@
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2095" t="inlineStr">
@@ -61482,7 +61482,7 @@
       </c>
       <c r="C2106" t="inlineStr">
         <is>
-          <t>DecitionUsefulness</t>
+          <t>DecisionUsefulness</t>
         </is>
       </c>
       <c r="D2106" t="inlineStr">
